--- a/nr-create-FrPractitionerRole/ig/ValueSet-fr-core-vs-organization-activity-field.xlsx
+++ b/nr-create-FrPractitionerRole/ig/ValueSet-fr-core-vs-organization-activity-field.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-11T15:44:52+00:00</t>
+    <t>2024-06-11T16:34:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-create-FrPractitionerRole/ig/ValueSet-fr-core-vs-organization-activity-field.xlsx
+++ b/nr-create-FrPractitionerRole/ig/ValueSet-fr-core-vs-organization-activity-field.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-11T16:34:47+00:00</t>
+    <t>2024-06-11T16:42:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-create-FrPractitionerRole/ig/ValueSet-fr-core-vs-organization-activity-field.xlsx
+++ b/nr-create-FrPractitionerRole/ig/ValueSet-fr-core-vs-organization-activity-field.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-11T16:42:33+00:00</t>
+    <t>2024-06-11T16:43:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
